--- a/AAII_Financials/Quarterly/AGBK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/AGBK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="92">
   <si>
     <t>AGBK</t>
   </si>
@@ -656,52 +656,54 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,29 +719,32 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>167000</v>
+      </c>
+      <c r="E8" s="3">
         <v>165400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>149900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
+        <v>187200</v>
+      </c>
+      <c r="H8" s="3">
         <v>192900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>150000</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -755,29 +760,32 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>87400</v>
+      </c>
+      <c r="E9" s="3">
         <v>69600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>49600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
+        <v>58900</v>
+      </c>
+      <c r="H9" s="3">
         <v>53900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>61100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -793,29 +801,32 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>79600</v>
+      </c>
+      <c r="E10" s="3">
         <v>95900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
+        <v>128200</v>
+      </c>
+      <c r="H10" s="3">
         <v>138900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>88900</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,8 +842,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -847,8 +861,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -885,8 +900,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -923,29 +941,32 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>1900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -961,29 +982,32 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E15" s="3">
         <v>10300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
+        <v>8900</v>
+      </c>
+      <c r="H15" s="3">
         <v>8200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>7200</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -999,8 +1023,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1012,29 +1039,30 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>148500</v>
+      </c>
+      <c r="E17" s="3">
         <v>122100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>109800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
+        <v>117800</v>
+      </c>
+      <c r="H17" s="3">
         <v>104700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>110300</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,29 +1078,32 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E18" s="3">
         <v>43300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>40100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
+        <v>69400</v>
+      </c>
+      <c r="H18" s="3">
         <v>88200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>39700</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1119,11 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1104,29 +1138,30 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-1500</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,29 +1177,32 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E21" s="3">
         <v>51700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>51300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
+        <v>76300</v>
+      </c>
+      <c r="H21" s="3">
         <v>97400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>48300</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
@@ -1180,8 +1218,11 @@
       <c r="N21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1218,29 +1259,32 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22200</v>
+      </c>
+      <c r="E23" s="3">
         <v>41400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>43200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
+        <v>67400</v>
+      </c>
+      <c r="H23" s="3">
         <v>89200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>39200</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1256,29 +1300,32 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="E24" s="3">
         <v>5700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
+        <v>18900</v>
+      </c>
+      <c r="H24" s="3">
         <v>27100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>7400</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1294,8 +1341,11 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1332,29 +1382,32 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E26" s="3">
         <v>35800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
+        <v>48400</v>
+      </c>
+      <c r="H26" s="3">
         <v>62200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>31900</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1370,29 +1423,32 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E27" s="3">
         <v>35800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>39000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
+        <v>48200</v>
+      </c>
+      <c r="H27" s="3">
         <v>61000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>31600</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,8 +1464,11 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1446,8 +1505,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1484,8 +1546,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1522,8 +1587,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1560,29 +1628,32 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>1500</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1598,29 +1669,32 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E33" s="3">
         <v>35800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>39000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
+        <v>48200</v>
+      </c>
+      <c r="H33" s="3">
         <v>61000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>31600</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1636,8 +1710,11 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1674,29 +1751,32 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E35" s="3">
         <v>35800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>39000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
+        <v>48200</v>
+      </c>
+      <c r="H35" s="3">
         <v>61000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>31600</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,34 +1792,37 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1838,11 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1771,8 +1857,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1787,29 +1874,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>145200</v>
+      </c>
+      <c r="E41" s="3">
         <v>192200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>59400</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="G41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3">
         <v>37300</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1825,29 +1913,32 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>423100</v>
+      </c>
+      <c r="E42" s="3">
         <v>602000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>658800</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>368700</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1863,29 +1954,32 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6802200</v>
+      </c>
+      <c r="E43" s="3">
         <v>6478000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5962600</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3">
         <v>3702500</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1901,8 +1995,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1939,29 +2036,32 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E45" s="3">
         <v>199200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>198000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>51900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1977,29 +2077,32 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7486100</v>
+      </c>
+      <c r="E46" s="3">
         <v>7471400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6878800</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="G46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3">
         <v>4160300</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2015,29 +2118,32 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1536200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1536400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1308300</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>259000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,29 +2159,32 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>58500</v>
+      </c>
+      <c r="E48" s="3">
         <v>56200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>55200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>45500</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2091,29 +2200,32 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E49" s="3">
         <v>42900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>33100</v>
       </c>
-      <c r="F49" s="3">
-        <v>0</v>
-      </c>
       <c r="G49" s="3">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
         <v>32200</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2129,8 +2241,11 @@
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2167,8 +2282,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2205,29 +2323,32 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>485900</v>
+      </c>
+      <c r="E52" s="3">
         <v>237200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>133000</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3">
         <v>140600</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2243,8 +2364,11 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2281,29 +2405,32 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9865100</v>
+      </c>
+      <c r="E54" s="3">
         <v>9621600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8671100</v>
       </c>
-      <c r="F54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="G54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3">
         <v>4772100</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2446,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2335,8 +2465,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2351,29 +2482,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3737400</v>
+      </c>
+      <c r="E57" s="3">
         <v>4256400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3852800</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>2716300</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2389,29 +2521,32 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>260700</v>
+      </c>
+      <c r="E58" s="3">
         <v>54800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>80900</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>62600</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2427,29 +2562,32 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>781000</v>
+      </c>
+      <c r="E59" s="3">
         <v>581100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>411200</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>141300</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,29 +2603,32 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4818400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4924700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4387000</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>2953400</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2503,29 +2644,32 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3545000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2986000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2722100</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>863000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2541,29 +2685,32 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>551200</v>
+      </c>
+      <c r="E62" s="3">
         <v>773900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>897600</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3">
         <v>521800</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2579,8 +2726,11 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2617,8 +2767,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2655,8 +2808,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2693,29 +2849,32 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8938700</v>
+      </c>
+      <c r="E66" s="3">
         <v>8729300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8076200</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="G66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3">
         <v>4371700</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +2890,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2747,8 +2909,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2785,8 +2948,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2823,8 +2989,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2861,8 +3030,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2899,29 +3071,32 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>74700</v>
+      </c>
+      <c r="E72" s="3">
         <v>35800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>20900</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>8500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2937,8 +3112,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2975,8 +3153,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3013,8 +3194,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3051,29 +3235,32 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>926300</v>
+      </c>
+      <c r="E76" s="3">
         <v>892300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>594900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H76" s="3">
         <v>412000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>381900</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,8 +3276,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3127,34 +3317,37 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3170,29 +3363,32 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E81" s="3">
         <v>35800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>39000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
+        <v>48200</v>
+      </c>
+      <c r="H81" s="3">
         <v>61000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>31600</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3208,8 +3404,11 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3224,16 +3423,17 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>-1500</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -3262,8 +3462,11 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3300,8 +3503,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3338,8 +3544,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3376,8 +3585,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3414,8 +3626,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3452,29 +3667,32 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-301300</v>
+      </c>
+      <c r="E89" s="3">
         <v>5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
+        <v>-167300</v>
+      </c>
+      <c r="H89" s="3">
         <v>-6600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>40600</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3490,8 +3708,11 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3506,29 +3727,30 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3544,8 +3766,11 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3582,8 +3807,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3620,29 +3848,32 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H94" s="3">
         <v>-8900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-4600</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,8 +3889,11 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3674,8 +3908,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3685,18 +3920,18 @@
       <c r="E96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3">
+        <v>500</v>
+      </c>
+      <c r="H96" s="3">
         <v>17600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>4100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
@@ -3712,8 +3947,11 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3750,8 +3988,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3788,8 +4029,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3826,29 +4070,32 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>124400</v>
+      </c>
+      <c r="E100" s="3">
         <v>236700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
+        <v>29800</v>
+      </c>
+      <c r="H100" s="3">
         <v>-29200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>126500</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +4111,11 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3902,29 +4152,32 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-188100</v>
+      </c>
+      <c r="E102" s="3">
         <v>225100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
+        <v>-142700</v>
+      </c>
+      <c r="H102" s="3">
         <v>-44700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>162500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
@@ -3938,6 +4191,9 @@
         <v>0</v>
       </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3">
         <v>0</v>
       </c>
     </row>
